--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -918,7 +918,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -968,13 +968,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -984,6 +984,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1331,7 +1334,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1905" y="5821680"/>
+          <a:off x="1905" y="6316980"/>
           <a:ext cx="13163550" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1713,7 +1716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" spans="1:4">
+    <row r="8" ht="84" customHeight="1" spans="1:4">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
@@ -1759,7 +1762,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1" spans="1:4">
+    <row r="13" ht="85" customHeight="1" spans="1:4">
       <c r="A13" s="9" t="s">
         <v>30</v>
       </c>
@@ -1769,29 +1772,29 @@
       <c r="C13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1" spans="1:4">
+    <row r="14" ht="109" customHeight="1" spans="1:4">
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="16" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1" spans="1:4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
@@ -1802,38 +1805,38 @@
       <c r="D16" s="4"/>
     </row>
     <row r="17" ht="45" customHeight="1" spans="1:4">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" spans="1:4">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:4">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1845,7 +1848,7 @@
     <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.590277777777778" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="56" orientation="portrait" horizontalDpi="600"/>
+  <pageSetup paperSize="9" scale="53" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -968,13 +968,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -986,7 +986,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1780,7 +1780,7 @@
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="22" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="9" t="s">

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -918,58 +918,55 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -980,31 +977,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1720,25 +1711,25 @@
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:4">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:4">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
@@ -1752,7 +1743,7 @@
       <c r="A12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -1772,7 +1763,7 @@
       <c r="C13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1780,21 +1771,21 @@
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1" spans="1:4">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
@@ -1805,38 +1796,38 @@
       <c r="D16" s="4"/>
     </row>
     <row r="17" ht="45" customHeight="1" spans="1:4">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" spans="1:4">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>投标费用审批单</t>
   </si>
@@ -104,7 +104,40 @@
     <t>{paymentRemark}</t>
   </si>
   <si>
-    <t>核准：{approvedBy}  会计：{accounting}    出纳：{cashier}   招投标部：{bidDept}  部门负责人：{manager}    经办人：{initor}</t>
+    <t>核准：</t>
+  </si>
+  <si>
+    <t>{approvedBy}</t>
+  </si>
+  <si>
+    <t>会计：</t>
+  </si>
+  <si>
+    <t>{accounting}</t>
+  </si>
+  <si>
+    <t>出纳：</t>
+  </si>
+  <si>
+    <t>{cashier}</t>
+  </si>
+  <si>
+    <t>招投标部：</t>
+  </si>
+  <si>
+    <t>{bidDept}</t>
+  </si>
+  <si>
+    <t>部门负责人：</t>
+  </si>
+  <si>
+    <t>{manager}</t>
+  </si>
+  <si>
+    <t>经办人：</t>
+  </si>
+  <si>
+    <t>{initor}</t>
   </si>
   <si>
     <t>基本信息</t>
@@ -177,12 +210,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -562,7 +594,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -595,47 +627,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -647,12 +638,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -668,6 +655,50 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -794,7 +825,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -806,34 +837,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -918,7 +949,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -931,70 +962,91 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1313,7 +1365,7 @@
       <xdr:rowOff>601980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>90805</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>601980</xdr:rowOff>
@@ -1326,7 +1378,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1905" y="6316980"/>
-          <a:ext cx="13163550" cy="0"/>
+          <a:ext cx="11815445" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1611,235 +1663,1029 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:M77"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="38.2083333333333" customWidth="1"/>
-    <col min="2" max="2" width="41.0666666666667" customWidth="1"/>
-    <col min="3" max="3" width="40.7083333333333" customWidth="1"/>
-    <col min="4" max="4" width="51.6" customWidth="1"/>
+    <col min="1" max="1" width="11.6" customWidth="1"/>
+    <col min="2" max="2" width="13.0416666666667" customWidth="1"/>
+    <col min="3" max="3" width="11.9583333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.0333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.2166666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.1083333333333" customWidth="1"/>
+    <col min="7" max="7" width="11.9583333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.7416666666667" customWidth="1"/>
+    <col min="9" max="9" width="12.3166666666667" customWidth="1"/>
+    <col min="10" max="10" width="13.2166666666667" customWidth="1"/>
+    <col min="11" max="11" width="11.2416666666667" customWidth="1"/>
+    <col min="12" max="12" width="14.4583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" customHeight="1" spans="1:4">
+    <row r="1" ht="54" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="35" customHeight="1" spans="1:5">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" ht="35" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" ht="45" customHeight="1" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="29"/>
+    </row>
+    <row r="3" ht="45" customHeight="1" spans="1:12">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" ht="45" customHeight="1" spans="1:4">
-      <c r="A4" s="9" t="s">
+      <c r="K3" s="11"/>
+      <c r="L3" s="17"/>
+    </row>
+    <row r="4" ht="45" customHeight="1" spans="1:12">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" ht="45" customHeight="1" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="17"/>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:12">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="K5" s="11"/>
+      <c r="L5" s="17"/>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:12">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" ht="45" customHeight="1" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="K6" s="11"/>
+      <c r="L6" s="17"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:12">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="K7" s="11"/>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" ht="84" customHeight="1" spans="1:12">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-    </row>
-    <row r="9" ht="52" customHeight="1" spans="1:4">
-      <c r="A9" s="18" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" ht="52" customHeight="1" spans="1:12">
+      <c r="A9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" ht="90" customHeight="1" spans="1:4">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="11" ht="35" customHeight="1" spans="1:4">
+      <c r="B9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1" spans="1:12">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" ht="35" customHeight="1" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" ht="45" customHeight="1" spans="1:4">
-      <c r="A12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" ht="85" customHeight="1" spans="1:4">
-      <c r="A13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" ht="109" customHeight="1" spans="1:4">
-      <c r="A14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="21" t="s">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="32"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" spans="1:12">
+      <c r="A12" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" ht="90" customHeight="1" spans="1:4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-    </row>
-    <row r="16" ht="35" customHeight="1" spans="1:4">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" ht="85" customHeight="1" spans="1:12">
+      <c r="A13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="17"/>
+    </row>
+    <row r="14" ht="109" customHeight="1" spans="1:12">
+      <c r="A14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="17"/>
+    </row>
+    <row r="15" ht="90" customHeight="1" spans="1:12">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="16" ht="35" customHeight="1" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="1:4">
-      <c r="A17" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="1:4">
-      <c r="A18" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1" spans="1:4">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="1:12">
+      <c r="A17" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="20"/>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="1:12">
+      <c r="A18" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="L18" s="24"/>
+    </row>
+    <row r="19" ht="13" customHeight="1" spans="1:12">
       <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="J20" s="27"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="J27" s="27"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="J28" s="27"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="J29" s="27"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="J30" s="27"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="J31" s="27"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="J34" s="27"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="J35" s="27"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="J36" s="27"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="J37" s="27"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="J39" s="27"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="J40" s="27"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="J41" s="27"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="J42" s="27"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="J43" s="27"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="J45" s="27"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="J46" s="27"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="J47" s="27"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="J48" s="27"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="J49" s="27"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="J50" s="27"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="J51" s="27"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="J52" s="27"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="J53" s="27"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="J54" s="27"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="J55" s="27"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="J56" s="27"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="J57" s="27"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="J58" s="27"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="J59" s="27"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="J60" s="27"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="J61" s="27"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="J62" s="27"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="J63" s="27"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="J64" s="27"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="J65" s="27"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="J66" s="27"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="J67" s="27"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="J68" s="27"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="J69" s="27"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="J70" s="27"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="J71" s="27"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="J72" s="27"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="J73" s="27"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="27"/>
+      <c r="D74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="J74" s="27"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="J75" s="27"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+  <mergeCells count="279">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="J73:L73"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="G74:I74"/>
+    <mergeCell ref="J74:L74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="A77:C77"/>
   </mergeCells>
   <pageMargins left="0.590277777777778" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="53" orientation="portrait" horizontalDpi="600"/>
+  <pageSetup paperSize="9" scale="59" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -1378,7 +1378,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1905" y="6316980"/>
-          <a:ext cx="11815445" cy="0"/>
+          <a:ext cx="12875260" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1667,17 +1667,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.6" customWidth="1"/>
-    <col min="2" max="2" width="13.0416666666667" customWidth="1"/>
-    <col min="3" max="3" width="11.9583333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.6416666666667" customWidth="1"/>
+    <col min="3" max="3" width="15.175" customWidth="1"/>
     <col min="4" max="4" width="13.0333333333333" customWidth="1"/>
     <col min="5" max="5" width="13.2166666666667" customWidth="1"/>
-    <col min="6" max="6" width="14.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="14.8166666666667" customWidth="1"/>
     <col min="7" max="7" width="11.9583333333333" customWidth="1"/>
-    <col min="8" max="8" width="13.7416666666667" customWidth="1"/>
-    <col min="9" max="9" width="12.3166666666667" customWidth="1"/>
-    <col min="10" max="10" width="13.2166666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.675" customWidth="1"/>
+    <col min="9" max="9" width="14.4583333333333" customWidth="1"/>
+    <col min="10" max="10" width="13.9166666666667" customWidth="1"/>
     <col min="11" max="11" width="11.2416666666667" customWidth="1"/>
-    <col min="12" max="12" width="14.4583333333333" customWidth="1"/>
+    <col min="12" max="12" width="16.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:12">

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -1660,9 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+  <sheetPr/>
   <dimension ref="A1:M77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2685,7 +2683,7 @@
     <mergeCell ref="A77:C77"/>
   </mergeCells>
   <pageMargins left="0.590277777777778" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="59" orientation="portrait" horizontalDpi="600"/>
+  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -216,9 +216,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -234,14 +241,14 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -250,6 +257,13 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -594,7 +608,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -721,16 +735,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF4874CB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -792,7 +797,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF4874CB"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
@@ -819,234 +824,228 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1316,6 +1315,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1377,8 +1381,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1905" y="6316980"/>
-          <a:ext cx="12875260" cy="0"/>
+          <a:off x="1905" y="7409180"/>
+          <a:ext cx="12808585" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1661,7 +1665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.6" customWidth="1"/>
@@ -1669,739 +1673,739 @@
     <col min="3" max="3" width="15.175" customWidth="1"/>
     <col min="4" max="4" width="13.0333333333333" customWidth="1"/>
     <col min="5" max="5" width="13.2166666666667" customWidth="1"/>
-    <col min="6" max="6" width="14.8166666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.9583333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.0333333333333" customWidth="1"/>
+    <col min="7" max="7" width="14.4583333333333" customWidth="1"/>
     <col min="8" max="8" width="17.675" customWidth="1"/>
-    <col min="9" max="9" width="14.4583333333333" customWidth="1"/>
-    <col min="10" max="10" width="13.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="16.6" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
     <col min="11" max="11" width="11.2416666666667" customWidth="1"/>
-    <col min="12" max="12" width="16.0666666666667" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="29"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="27"/>
     </row>
     <row r="3" ht="45" customHeight="1" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="11" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="17"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="18"/>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:12">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="11" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="17"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="18"/>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:12">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="11" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="K5" s="12"/>
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" ht="71" customHeight="1" spans="1:12">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="11" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="17"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="11" t="s">
+      <c r="H7" s="10"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="K7" s="12"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" ht="144" customHeight="1" spans="1:12">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="10" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" ht="52" customHeight="1" spans="1:12">
-      <c r="A9" s="13" t="s">
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="52" customHeight="1" spans="1:12">
+      <c r="A9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:12">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:12">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="32"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" ht="45" customHeight="1" spans="1:12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="11" t="s">
+      <c r="H12" s="10"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" ht="85" customHeight="1" spans="1:12">
-      <c r="A13" s="8" t="s">
+      <c r="K12" s="12"/>
+      <c r="L12" s="18"/>
+    </row>
+    <row r="13" ht="197" customHeight="1" spans="1:12">
+      <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="11" t="s">
+      <c r="H13" s="10"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" ht="109" customHeight="1" spans="1:12">
-      <c r="A14" s="8" t="s">
+      <c r="K13" s="12"/>
+      <c r="L13" s="18"/>
+    </row>
+    <row r="14" ht="199" customHeight="1" spans="1:12">
+      <c r="A14" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="10" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="8" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="10"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="17"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="18"/>
     </row>
     <row r="15" ht="90" customHeight="1" spans="1:12">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:12">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="28"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="26"/>
     </row>
     <row r="17" ht="45" customHeight="1" spans="1:12">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="19" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="19" t="s">
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="20" t="s">
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" ht="45" customHeight="1" spans="1:12">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="22" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="22" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="23"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="23" t="s">
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="23"/>
-      <c r="L18" s="24"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:12">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="J20" s="27"/>
+      <c r="A20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="J21" s="27"/>
+      <c r="A21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="J23" s="27"/>
+      <c r="A23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="J24" s="27"/>
+      <c r="A24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="J25" s="27"/>
+      <c r="A25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="J26" s="27"/>
+      <c r="A26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="J27" s="27"/>
+      <c r="A27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="J28" s="27"/>
+      <c r="A28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="J28" s="25"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="J29" s="27"/>
+      <c r="A29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="J30" s="27"/>
+      <c r="A30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="J31" s="27"/>
+      <c r="A31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="J32" s="27"/>
+      <c r="A32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="J33" s="27"/>
+      <c r="A33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="J34" s="27"/>
+      <c r="A34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="J35" s="27"/>
+      <c r="A35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="J36" s="27"/>
+      <c r="A36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="J36" s="25"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="J37" s="27"/>
+      <c r="A37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="J38" s="27"/>
+      <c r="A38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="J38" s="25"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="J39" s="27"/>
+      <c r="A39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="J40" s="27"/>
+      <c r="A40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="J41" s="27"/>
+      <c r="A41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="J41" s="25"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="J42" s="27"/>
+      <c r="A42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="J42" s="25"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="J43" s="27"/>
+      <c r="A43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="J44" s="27"/>
+      <c r="A44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="J44" s="25"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="J45" s="27"/>
+      <c r="A45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="J45" s="25"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="J46" s="27"/>
+      <c r="A46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="J47" s="27"/>
+      <c r="A47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="J47" s="25"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="J48" s="27"/>
+      <c r="A48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="J48" s="25"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="J49" s="27"/>
+      <c r="A49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="J50" s="27"/>
+      <c r="A50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="J50" s="25"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="J51" s="27"/>
+      <c r="A51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="J51" s="25"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="J52" s="27"/>
+      <c r="A52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="J52" s="25"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="J53" s="27"/>
+      <c r="A53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="J53" s="25"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="J54" s="27"/>
+      <c r="A54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="J55" s="27"/>
+      <c r="A55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="J55" s="25"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="J56" s="27"/>
+      <c r="A56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="J56" s="25"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="J57" s="27"/>
+      <c r="A57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="J58" s="27"/>
+      <c r="A58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="J59" s="27"/>
+      <c r="A59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="J60" s="27"/>
+      <c r="A60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="J61" s="27"/>
+      <c r="A61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="J62" s="27"/>
+      <c r="A62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="J62" s="25"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="J63" s="27"/>
+      <c r="A63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="J63" s="25"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="J64" s="27"/>
+      <c r="A64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="J64" s="25"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="J65" s="27"/>
+      <c r="A65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="J65" s="25"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="J66" s="27"/>
+      <c r="A66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="J66" s="25"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="J67" s="27"/>
+      <c r="A67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="J67" s="25"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="27"/>
-      <c r="D68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="J68" s="27"/>
+      <c r="A68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="J69" s="27"/>
+      <c r="A69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="J70" s="27"/>
+      <c r="A70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="J70" s="25"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="J71" s="27"/>
+      <c r="A71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="J71" s="25"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="J72" s="27"/>
+      <c r="A72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="J72" s="25"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="27"/>
-      <c r="D73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="J73" s="27"/>
+      <c r="A73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="J73" s="25"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="J74" s="27"/>
+      <c r="A74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="J74" s="25"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="J75" s="27"/>
+      <c r="A75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="J75" s="25"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="27"/>
+      <c r="A76" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="279">
+  <mergeCells count="278">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:C3"/>
@@ -2680,9 +2684,8 @@
     <mergeCell ref="D76:F76"/>
     <mergeCell ref="G76:I76"/>
     <mergeCell ref="J76:L76"/>
-    <mergeCell ref="A77:C77"/>
   </mergeCells>
-  <pageMargins left="0.590277777777778" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.590277777777778" right="0.590277777777778" top="0.747916666666667" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
   <drawing r:id="rId1"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/BidFeeTemplate.xlsx
@@ -1381,7 +1381,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1905" y="7409180"/>
+          <a:off x="1905" y="8374380"/>
           <a:ext cx="12808585" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1737,7 +1737,7 @@
       <c r="K3" s="12"/>
       <c r="L3" s="18"/>
     </row>
-    <row r="4" ht="45" customHeight="1" spans="1:12">
+    <row r="4" ht="83" customHeight="1" spans="1:12">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
@@ -1803,7 +1803,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="18"/>
     </row>
-    <row r="7" ht="45" customHeight="1" spans="1:12">
+    <row r="7" ht="51" customHeight="1" spans="1:12">
       <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
@@ -1825,7 +1825,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="18"/>
     </row>
-    <row r="8" ht="144" customHeight="1" spans="1:12">
+    <row r="8" ht="176" customHeight="1" spans="1:12">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
